--- a/logs/Jun_15_full_log/6_15_LHS_HRP_all_res.xlsx
+++ b/logs/Jun_15_full_log/6_15_LHS_HRP_all_res.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\logs\Jun_15_full_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88838812-7779-456B-8BA0-E4BAC220E48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9E25A1-8040-4FF9-BCF1-ED4E17AA7A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -59,6 +59,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -99,11 +106,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6349,10 +6357,10 @@
       <c r="A259">
         <v>1</v>
       </c>
-      <c r="B259">
+      <c r="B259" s="2">
         <v>0.99532202000000003</v>
       </c>
-      <c r="C259">
+      <c r="C259" s="2">
         <v>7.9112929999999998E-2</v>
       </c>
       <c r="D259">
@@ -6364,7 +6372,7 @@
       <c r="F259">
         <v>0.62131288343558388</v>
       </c>
-      <c r="G259">
+      <c r="G259" s="2">
         <v>10175.758883248731</v>
       </c>
     </row>
@@ -6372,10 +6380,10 @@
       <c r="A260">
         <v>1</v>
       </c>
-      <c r="B260">
+      <c r="B260" s="2">
         <v>0.99532202000000003</v>
       </c>
-      <c r="C260">
+      <c r="C260" s="2">
         <v>7.9112929999999998E-2</v>
       </c>
       <c r="D260">
@@ -6387,7 +6395,7 @@
       <c r="F260">
         <v>0.61363679183073616</v>
       </c>
-      <c r="G260">
+      <c r="G260" s="2">
         <v>10077.692893401019</v>
       </c>
     </row>
@@ -6395,10 +6403,10 @@
       <c r="A261">
         <v>1</v>
       </c>
-      <c r="B261">
+      <c r="B261" s="2">
         <v>0.99532202000000003</v>
       </c>
-      <c r="C261">
+      <c r="C261" s="2">
         <v>7.9112929999999998E-2</v>
       </c>
       <c r="D261">
@@ -6410,7 +6418,7 @@
       <c r="F261">
         <v>0.5925096967601694</v>
       </c>
-      <c r="G261">
+      <c r="G261" s="2">
         <v>10054.75634517767</v>
       </c>
     </row>
@@ -6418,10 +6426,10 @@
       <c r="A262">
         <v>1</v>
       </c>
-      <c r="B262">
+      <c r="B262" s="2">
         <v>0.99532202000000003</v>
       </c>
-      <c r="C262">
+      <c r="C262" s="2">
         <v>7.9112929999999998E-2</v>
       </c>
       <c r="D262">
@@ -6433,7 +6441,7 @@
       <c r="F262">
         <v>0.55760254931255648</v>
       </c>
-      <c r="G262">
+      <c r="G262" s="2">
         <v>9830.8637055837571</v>
       </c>
     </row>
